--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486500_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486500_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8486</v>
+        <v>4.936</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7785</v>
+        <v>2.7128</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0701</v>
+        <v>2.2232</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7556</v>
+        <v>4.6095</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4265</v>
+        <v>3.1233</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3291</v>
+        <v>1.4861</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3158</v>
+        <v>4.0455</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6274</v>
+        <v>3.0111</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6885</v>
+        <v>1.0343</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4398</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2009</v>
+        <v>0.1122</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6407</v>
+        <v>0.4518</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8755</v>
+        <v>-0.1085</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5502</v>
+        <v>-0.2451</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3253</v>
+        <v>0.1367</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1229</v>
+        <v>4.2802</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9305</v>
+        <v>1.5492</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1924</v>
+        <v>2.7311</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6095</v>
+        <v>2.7556</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1233</v>
+        <v>1.4265</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4861</v>
+        <v>1.3291</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0455</v>
+        <v>2.3158</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0111</v>
+        <v>1.6274</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0343</v>
+        <v>0.6885</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.4398</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1122</v>
+        <v>-0.2009</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4518</v>
+        <v>0.6407</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9216</v>
+        <v>1.3071</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0274</v>
+        <v>0.3209</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1059</v>
+        <v>0.9863</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.351</v>
+        <v>3.2798</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1859</v>
+        <v>-0.3477</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1651</v>
+        <v>3.6274</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2539</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5173</v>
+        <v>0.4461</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0707</v>
+        <v>0.5372</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5534</v>
+        <v>-0.091</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1709</v>
+        <v>3.1459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9408</v>
+        <v>0.2811</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2301</v>
+        <v>2.8649</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1548</v>
+        <v>3.7165</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4927</v>
+        <v>0.8941</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3379</v>
+        <v>2.8225</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0698</v>
+        <v>2.5692</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0698</v>
+        <v>-0.0151</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5843</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2247</v>
+        <v>1.1474</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5626</v>
+        <v>0.9091</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3379</v>
+        <v>0.2382</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9576</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R5" t="n">
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0585</v>
+        <v>-0.0682</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0106</v>
+        <v>0.1719</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0478</v>
+        <v>-0.2401</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0513</v>
+        <v>2.6874</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0323</v>
+        <v>0.519</v>
       </c>
       <c r="F6" t="n">
-        <v>3.019</v>
+        <v>2.1684</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7165</v>
+        <v>0.1548</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8941</v>
+        <v>0.4927</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8225</v>
+        <v>-0.3379</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5692</v>
+        <v>-0.0698</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0151</v>
+        <v>-0.0698</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5843</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1474</v>
+        <v>0.2247</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9091</v>
+        <v>0.5626</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2382</v>
+        <v>-0.3379</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1628</v>
+        <v>0.575</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0769</v>
+        <v>0.5888</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0859</v>
+        <v>-0.0138</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9886</v>
+        <v>1.326</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9292</v>
+        <v>-1.3452</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9177</v>
+        <v>2.6712</v>
       </c>
       <c r="G7" t="n">
         <v>-1.2498</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.132</v>
+        <v>0.2055</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>0.0361</v>
       </c>
       <c r="U7" t="n">
-        <v>0.416</v>
+        <v>0.1694</v>
       </c>
       <c r="V7" t="n">
         <v>0.1952</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4339</v>
+        <v>1.0563</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1577</v>
+        <v>1.4923</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7238</v>
+        <v>-0.436</v>
       </c>
       <c r="G8" t="n">
-        <v>1.282</v>
+        <v>0.6615</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3625</v>
+        <v>2.3023</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0805</v>
+        <v>-1.6407</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8193</v>
+        <v>1.6697</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1164</v>
+        <v>2.7191</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7029</v>
+        <v>-1.0494</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5372</v>
+        <v>-1.0082</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2461</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7834</v>
+        <v>-0.5913</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1081</v>
+        <v>-0.2578</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6165</v>
+        <v>-0.2199</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4916</v>
+        <v>-0.0379</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4232</v>
+        <v>1.0466</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.352</v>
+        <v>1.493</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7752</v>
+        <v>-0.4464</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5599</v>
+        <v>1.282</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0379</v>
+        <v>1.3625</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.5978</v>
+        <v>-0.0805</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6362</v>
+        <v>2.8193</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3057</v>
+        <v>1.1164</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.942</v>
+        <v>1.7029</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9237</v>
+        <v>-1.5372</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2679</v>
+        <v>0.2461</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6558</v>
+        <v>-1.7834</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7449</v>
+        <v>-0.4954</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2139</v>
+        <v>-0.2812</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9588</v>
+        <v>-0.2142</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5857</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5857</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0595</v>
+        <v>0.6108</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6847</v>
+        <v>-2.6505</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7442</v>
+        <v>3.2613</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6615</v>
+        <v>0.8001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3023</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6407</v>
+        <v>0.1856</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6697</v>
+        <v>-0.3138</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7191</v>
+        <v>-0.4102</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0494</v>
+        <v>0.0964</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0082</v>
+        <v>1.1139</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4169</v>
+        <v>1.0247</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5913</v>
+        <v>0.0892</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3735</v>
+        <v>-0.3845</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0274</v>
+        <v>-0.3569</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3461</v>
+        <v>-0.0277</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4297</v>
+        <v>0.1959</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3211</v>
+        <v>-1.2402</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8914</v>
+        <v>1.4361</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8001</v>
+        <v>-1.5599</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6143999999999999</v>
+        <v>2.0379</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1856</v>
+        <v>-3.5978</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3138</v>
+        <v>-0.6362</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4102</v>
+        <v>2.3057</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0964</v>
+        <v>-2.942</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1139</v>
+        <v>-0.9237</v>
       </c>
       <c r="N11" t="n">
-        <v>1.0247</v>
+        <v>-0.2679</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0892</v>
+        <v>-0.6558</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.425</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0274</v>
+        <v>-0.1021</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3975</v>
+        <v>0.6198</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1952</v>
+        <v>0.5857</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1952</v>
+        <v>0.5857</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0693</v>
+        <v>-2.0481</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3689</v>
+        <v>-2.0395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2996</v>
+        <v>-0.0086</v>
       </c>
       <c r="G12" t="n">
         <v>-0.011</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>0.834</v>
+        <v>-0.1448</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9421</v>
+        <v>0.2716</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1082</v>
+        <v>-0.4164</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3698</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.8319</v>
+        <v>20.5168</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2607999999999993</v>
+        <v>0.4243000000000001</v>
       </c>
       <c r="F13" t="n">
         <v>20.0926</v>
@@ -1438,16 +1438,16 @@
         <v>11.5272</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6217999999999997</v>
+        <v>-0.6218000000000004</v>
       </c>
       <c r="J13" t="n">
-        <v>9.042200000000001</v>
+        <v>9.042199999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>8.3208</v>
+        <v>8.320799999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7211999999999994</v>
+        <v>0.7211999999999996</v>
       </c>
       <c r="M13" t="n">
         <v>1.8636</v>
@@ -1459,7 +1459,7 @@
         <v>-1.3429</v>
       </c>
       <c r="P13" t="n">
-        <v>3.262700000000001</v>
+        <v>3.2627</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.2254</v>
@@ -1468,13 +1468,13 @@
         <v>18.4882</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9071999999999997</v>
+        <v>1.592099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.03609999999999969</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8710999999999999</v>
+        <v>0.8711000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.7565</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2598</v>
+        <v>3.5331</v>
       </c>
       <c r="E14" t="n">
-        <v>3.212</v>
+        <v>1.4052</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0478</v>
+        <v>2.1279</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3106</v>
+        <v>1.9557</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4657</v>
+        <v>-0.6692</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7763</v>
+        <v>2.6249</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1603</v>
+        <v>2.5264</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1952</v>
+        <v>0.4777</v>
       </c>
       <c r="L14" t="n">
-        <v>2.9651</v>
+        <v>2.0488</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8497</v>
+        <v>-0.5707</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6608</v>
+        <v>-1.1468</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1889</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0792</v>
+        <v>-0.0544</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1392</v>
+        <v>-0.0336</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9399</v>
+        <v>-0.0207</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5138</v>
+        <v>2.5874</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2935</v>
+        <v>2.0944</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2204</v>
+        <v>0.493</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9557</v>
+        <v>1.3106</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6692</v>
+        <v>-1.4657</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6249</v>
+        <v>2.7763</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5264</v>
+        <v>3.1603</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4777</v>
+        <v>0.1952</v>
       </c>
       <c r="L15" t="n">
-        <v>2.0488</v>
+        <v>2.9651</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5707</v>
+        <v>-1.8497</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1468</v>
+        <v>-1.6608</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.1889</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0737</v>
+        <v>0.4068</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1454</v>
+        <v>0.0216</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0717</v>
+        <v>0.3851</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3318</v>
+        <v>0.6979</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3436</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0118</v>
+        <v>0.019</v>
       </c>
       <c r="G16" t="n">
         <v>1.5217</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1575</v>
+        <v>0.5236</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1935</v>
+        <v>0.1418</v>
       </c>
       <c r="U16" t="n">
-        <v>0.351</v>
+        <v>0.3818</v>
       </c>
       <c r="V16" t="n">
         <v>-1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9399</v>
+        <v>-0.5714</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7488</v>
+        <v>-0.3832</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8088</v>
+        <v>-0.1882</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9316</v>
+        <v>-1.043</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0041</v>
+        <v>-1.9466</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0725</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6444</v>
+        <v>0.8577</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6078</v>
+        <v>-0.6173</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0366</v>
+        <v>1.475</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2872</v>
+        <v>-1.9007</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3963</v>
+        <v>-1.3293</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1091</v>
+        <v>-0.5714</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.4855</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0168</v>
+        <v>-0.1959</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8839</v>
+        <v>-0.2896</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3698</v>
+        <v>0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3698</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0415</v>
+        <v>-0.5894</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6068</v>
+        <v>-1.8605</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4348</v>
+        <v>1.2712</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.043</v>
+        <v>-1.9316</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9466</v>
+        <v>-2.0041</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9036999999999999</v>
+        <v>0.0725</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8577</v>
+        <v>-0.6444</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6173</v>
+        <v>-0.6078</v>
       </c>
       <c r="L18" t="n">
-        <v>1.475</v>
+        <v>-0.0366</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9007</v>
+        <v>-1.2872</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3293</v>
+        <v>-1.3963</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5714</v>
+        <v>0.1091</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9556</v>
+        <v>-0.5501</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4194</v>
+        <v>-0.1286</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5362</v>
+        <v>-0.4215</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7395</v>
+        <v>0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3904</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5215</v>
+        <v>-1.5292</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.448</v>
+        <v>-2.6716</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9266</v>
+        <v>1.1423</v>
       </c>
       <c r="G19" t="n">
         <v>1.5372</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0136</v>
+        <v>-0.0213</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4062</v>
+        <v>0.1827</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4198</v>
+        <v>-0.204</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7501</v>
+        <v>-1.8464</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.796</v>
+        <v>-3.4608</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0459</v>
+        <v>1.6144</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1354</v>
@@ -2014,13 +2014,13 @@
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1678</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2139</v>
+        <v>0.1214</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3816</v>
+        <v>-0.0499</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5921</v>
+        <v>-4.5491</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2587</v>
+        <v>-4.3842</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3334</v>
+        <v>-0.165</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5906</v>
+        <v>-1.4265</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1976</v>
+        <v>-0.5627</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7881</v>
+        <v>-0.8638</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3529</v>
+        <v>-2.1022</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7149</v>
+        <v>-0.7268</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0678</v>
+        <v>-1.3754</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2377</v>
+        <v>0.6757</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5173</v>
+        <v>0.1641</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7204</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.305</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0016</v>
+        <v>-0.0574</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2692</v>
+        <v>-0.1069</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2708</v>
+        <v>0.0496</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.695</v>
+        <v>-1.3252</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.695</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9884</v>
+        <v>-4.7116</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6077</v>
+        <v>-2.594</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3807</v>
+        <v>-2.1176</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4265</v>
+        <v>-1.5906</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5627</v>
+        <v>0.1976</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8638</v>
+        <v>-1.7881</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1022</v>
+        <v>-0.3529</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7268</v>
+        <v>0.7149</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3754</v>
+        <v>-1.0678</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6757</v>
+        <v>-1.2377</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1641</v>
+        <v>-0.5173</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.7204</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7401</v>
+        <v>-1.305</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4967</v>
+        <v>-0.1211</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3305</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1662</v>
+        <v>-0.055</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3252</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4748</v>
+        <v>-6.3553</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1995</v>
+        <v>-4.9408</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2752</v>
+        <v>-1.4145</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1988</v>
+        <v>-5.9049</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6545</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5443</v>
+        <v>-5.3238</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.134</v>
+        <v>-4.8002</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9061</v>
+        <v>0.1857</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2279</v>
+        <v>-4.9859</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0648</v>
+        <v>-1.1047</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7484</v>
+        <v>-0.7668</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3164</v>
+        <v>-0.3379</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6234</v>
+        <v>0.027</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8904</v>
+        <v>-0.1406</v>
       </c>
       <c r="U23" t="n">
-        <v>0.267</v>
+        <v>0.1676</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6289</v>
+        <v>-6.4978</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2761</v>
+        <v>-3.976</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3528</v>
+        <v>-2.5218</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.9049</v>
+        <v>-3.1988</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-1.6545</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.3238</v>
+        <v>-1.5443</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.8002</v>
+        <v>-1.134</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1857</v>
+        <v>-0.9061</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.9859</v>
+        <v>-0.2279</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1047</v>
+        <v>-2.0648</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7668</v>
+        <v>-0.7484</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3379</v>
+        <v>-1.3164</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2466</v>
+        <v>-0.6465</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4759</v>
+        <v>-0.6669</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2293</v>
+        <v>0.0204</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2362,10 +2362,10 @@
         <v>-19.8318</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.0925</v>
+        <v>-20.0926</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2607999999999999</v>
+        <v>0.260699999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-10.9056</v>
@@ -2374,28 +2374,28 @@
         <v>-11.5271</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6216999999999979</v>
+        <v>0.6216999999999986</v>
       </c>
       <c r="J25" t="n">
         <v>-1.8634</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.206199999999999</v>
+        <v>-3.2062</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3429</v>
+        <v>1.342899999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-9.042199999999999</v>
+        <v>-9.042200000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.3207</v>
+        <v>-8.320699999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-0.7214</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.2627</v>
+        <v>-3.262700000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.488</v>
@@ -2404,13 +2404,13 @@
         <v>15.2254</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9073999999999997</v>
+        <v>-0.9074</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8712</v>
+        <v>-0.8711</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.03639999999999993</v>
+        <v>-0.03619999999999995</v>
       </c>
       <c r="V25" t="n">
         <v>-4.7566</v>
